--- a/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T14:36:19+00:00</t>
+    <t>2026-08-14T12:00:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:00:06+00:00</t>
+    <t>2026-08-14T14:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -55,7 +55,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T14:57:39+00:00</t>
+    <t>2026-08-20T08:45:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,13 +103,13 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-related-person</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-related-person|0.1.0</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-cda-related-entity</t>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-related-entity|0.1.0</t>
   </si>
   <si>
     <t>FRLMRelatedPerson</t>
@@ -169,7 +169,7 @@
     <t>relatedEntity.telecom</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-related-person-document</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0</t>
   </si>
   <si>
     <t>RelatedPerson</t>

--- a/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -9,12 +9,15 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Mapping Table 0" r:id="rId4" sheetId="2"/>
     <sheet name="Mapping Table 1" r:id="rId5" sheetId="3"/>
+    <sheet name="Mapping Table 2" r:id="rId6" sheetId="4"/>
+    <sheet name="Mapping Table 3" r:id="rId7" sheetId="5"/>
+    <sheet name="Mapping Table 4" r:id="rId8" sheetId="6"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
   <si>
     <t>Property</t>
   </si>
@@ -37,6 +40,9 @@
     <t>Name</t>
   </si>
   <si>
+    <t>FRRelatedPersonLMCDAFHIR</t>
+  </si>
+  <si>
     <t>Title</t>
   </si>
   <si>
@@ -52,10 +58,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T08:45:34+00:00</t>
+    <t>2026-08-31T15:12:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -103,7 +112,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/fr-lm-related-person|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMRelatedPerson|0.1.0</t>
   </si>
   <si>
     <t/>
@@ -118,55 +127,79 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>RelatedEntity</t>
+  </si>
+  <si>
     <t>relatedEntity</t>
   </si>
   <si>
+    <t>FRLMRelatedPerson.relationship</t>
+  </si>
+  <si>
+    <t>RelatedEntity.code</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.address</t>
+  </si>
+  <si>
+    <t>RelatedEntity.addr</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.telecom</t>
+  </si>
+  <si>
+    <t>RelatedEntity.telecom</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-assigned-person|0.1.0</t>
+  </si>
+  <si>
     <t>FRLMRelatedPerson.name</t>
   </si>
   <si>
-    <t>relatedEntity.relatedPerson.name</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.name.family</t>
-  </si>
-  <si>
-    <t>relatedEntity.relatedPerson.name.family</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.name.given</t>
-  </si>
-  <si>
-    <t>relatedEntity.relatedPerson.name.given</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.name.prefix</t>
-  </si>
-  <si>
-    <t>relatedEntity.relatedPerson.name.prefix</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.name.suffix</t>
-  </si>
-  <si>
-    <t>relatedEntity.relatedPerson.name.suffix</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.relationship</t>
-  </si>
-  <si>
-    <t>relatedEntity.code</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.address</t>
-  </si>
-  <si>
-    <t>relatedEntity.addr</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.telecom</t>
-  </si>
-  <si>
-    <t>relatedEntity.telecom</t>
+    <t>Person.name</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHumanName|0.1.0</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-name|0.1.0</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.use</t>
+  </si>
+  <si>
+    <t>PN.use</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.family</t>
+  </si>
+  <si>
+    <t>PN.item.family</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.given</t>
+  </si>
+  <si>
+    <t>PN.item.given</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.prefix</t>
+  </si>
+  <si>
+    <t>PN.item.prefix</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.suffix</t>
+  </si>
+  <si>
+    <t>PN.item.suffix</t>
+  </si>
+  <si>
+    <t>FRLMHumanName.period</t>
+  </si>
+  <si>
+    <t>PN.validTime</t>
   </si>
   <si>
     <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0</t>
@@ -184,6 +217,63 @@
     <t>RelatedPerson.name</t>
   </si>
   <si>
+    <t>FRLMRelatedPerson.subject</t>
+  </si>
+  <si>
+    <t>RelatedPerson.patient</t>
+  </si>
+  <si>
+    <t>RelatedPerson.relationship</t>
+  </si>
+  <si>
+    <t>RelatedPerson.address</t>
+  </si>
+  <si>
+    <t>RelatedPerson.telecom</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.gender</t>
+  </si>
+  <si>
+    <t>RelatedPerson.gender</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.birthDate</t>
+  </si>
+  <si>
+    <t>RelatedPerson.birthDate</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.photo</t>
+  </si>
+  <si>
+    <t>RelatedPerson.photo</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.period</t>
+  </si>
+  <si>
+    <t>RelatedPerson.period</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.communication</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.communication.language</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.language</t>
+  </si>
+  <si>
+    <t>FRLMRelatedPerson.communication.preferred</t>
+  </si>
+  <si>
+    <t>RelatedPerson.communication.preferred</t>
+  </si>
+  <si>
     <t>RelatedPerson.name.family</t>
   </si>
   <si>
@@ -194,63 +284,6 @@
   </si>
   <si>
     <t>RelatedPerson.name.suffix</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.subject</t>
-  </si>
-  <si>
-    <t>RelatedPerson.patient</t>
-  </si>
-  <si>
-    <t>RelatedPerson.relationship</t>
-  </si>
-  <si>
-    <t>RelatedPerson.address</t>
-  </si>
-  <si>
-    <t>RelatedPerson.telecom</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.gender</t>
-  </si>
-  <si>
-    <t>RelatedPerson.gender</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.birthDate</t>
-  </si>
-  <si>
-    <t>RelatedPerson.birthDate</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.photo</t>
-  </si>
-  <si>
-    <t>RelatedPerson.photo</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.period</t>
-  </si>
-  <si>
-    <t>RelatedPerson.period</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.communication</t>
-  </si>
-  <si>
-    <t>RelatedPerson.communication</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.communication.language</t>
-  </si>
-  <si>
-    <t>RelatedPerson.communication.language</t>
-  </si>
-  <si>
-    <t>FRLMRelatedPerson.communication.preferred</t>
-  </si>
-  <si>
-    <t>RelatedPerson.communication.preferred</t>
   </si>
 </sst>
 </file>
@@ -419,79 +452,83 @@
       <c r="A4" t="s" s="2">
         <v>6</v>
       </c>
-      <c r="B4" s="2"/>
+      <c r="B4" t="s" s="2">
+        <v>7</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>11</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>12</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
@@ -502,159 +539,96 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>33</v>
-      </c>
-      <c r="E3" s="2"/>
+        <v>35</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>41</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>43</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="E11" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
@@ -663,53 +637,458 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
         <v>27</v>
-      </c>
-      <c r="E1" t="s" s="1">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s" s="2">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>47</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
         <v>51</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>52</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E16"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D4" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D5" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D6" t="s" s="2">
+        <v>66</v>
+      </c>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="B7" s="2"/>
+      <c r="C7" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s" s="2">
+        <v>67</v>
+      </c>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>39</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s" s="2">
+        <v>68</v>
+      </c>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s" s="2">
+        <v>69</v>
+      </c>
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>70</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s" s="2">
+        <v>71</v>
+      </c>
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D11" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="B12" s="2"/>
+      <c r="C12" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="B13" s="2"/>
+      <c r="C13" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="B14" s="2"/>
+      <c r="C14" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D14" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="B15" s="2"/>
+      <c r="C15" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B16" s="2"/>
+      <c r="C16" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D16" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E16" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>26</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="D1" t="s" s="1">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C2" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="D2" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="E2" t="s" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>84</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -719,220 +1098,38 @@
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="E6" s="2"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D7" t="s" s="2">
-        <v>56</v>
-      </c>
-      <c r="E7" s="2"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B8" s="2"/>
-      <c r="C8" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D8" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="E8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" s="2"/>
-      <c r="C9" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s" s="2">
-        <v>58</v>
-      </c>
-      <c r="E9" s="2"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D10" t="s" s="2">
-        <v>60</v>
-      </c>
-      <c r="E10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D11" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="E11" s="2"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D12" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="E12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D13" t="s" s="2">
-        <v>63</v>
-      </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>64</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D14" t="s" s="2">
-        <v>65</v>
-      </c>
-      <c r="E14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>66</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s" s="2">
-        <v>67</v>
-      </c>
-      <c r="E15" s="2"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>68</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D16" t="s" s="2">
-        <v>69</v>
-      </c>
-      <c r="E16" s="2"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>70</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s" s="2">
-        <v>71</v>
-      </c>
-      <c r="E17" s="2"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>72</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="B19" s="2"/>
-      <c r="C19" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E19" s="2"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="B20" s="2"/>
-      <c r="C20" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E20" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
+++ b/main/ig/FRRelatedPersonLMCDAFHIR.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="89">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T15:12:23+00:00</t>
+    <t>2026-09-04T14:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>FRLMRelatedPerson.name</t>
+  </si>
+  <si>
+    <t>FRLMHumanName</t>
   </si>
   <si>
     <t>Person.name</t>
@@ -678,12 +681,14 @@
       <c r="A3" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B3" s="2"/>
+      <c r="B3" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2"/>
     </row>
@@ -716,7 +721,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -725,7 +730,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -733,79 +738,79 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B7" s="2"/>
       <c r="C7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="2"/>
       <c r="C8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -847,7 +852,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -862,20 +867,20 @@
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" s="2"/>
     </row>
@@ -883,25 +888,27 @@
       <c r="A5" t="s" s="2">
         <v>44</v>
       </c>
-      <c r="B5" s="2"/>
+      <c r="B5" t="s" s="2">
+        <v>45</v>
+      </c>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E6" s="2"/>
     </row>
@@ -914,7 +921,7 @@
         <v>34</v>
       </c>
       <c r="D7" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E7" s="2"/>
     </row>
@@ -927,7 +934,7 @@
         <v>34</v>
       </c>
       <c r="D8" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E8" s="2"/>
     </row>
@@ -940,98 +947,98 @@
         <v>34</v>
       </c>
       <c r="D9" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2"/>
       <c r="C10" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D10" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D11" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D12" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D14" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D15" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D16" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1064,7 +1071,7 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B2" t="s" s="2">
         <v>31</v>
@@ -1073,7 +1080,7 @@
         <v>31</v>
       </c>
       <c r="D2" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E2" t="s" s="2">
         <v>31</v>
@@ -1081,53 +1088,53 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="D6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E6" s="2"/>
     </row>
